--- a/backend/real_data/teachers_information_3.xlsx
+++ b/backend/real_data/teachers_information_3.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DATA\school_timeTable_v1.9\backend\real_data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DATA\school_timeTable_v2.0\backend\real_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68437929-E197-4E17-8927-CC31877953C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6414B96E-65FF-4405-BADB-6979DC21834E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="254">
   <si>
     <t>Mã Giáo Viên</t>
   </si>
@@ -779,6 +779,9 @@
   </si>
   <si>
     <t>TO12-12A4, TO12-12A9, TO11-11A1, TO11-11A7</t>
+  </si>
+  <si>
+    <t>12A5</t>
   </si>
 </sst>
 </file>
@@ -788,7 +791,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="30">
+  <fonts count="31">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -980,6 +983,14 @@
       <name val="Cambria"/>
       <family val="1"/>
       <scheme val="major"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="24">
@@ -1274,7 +1285,7 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyFont="0"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1303,6 +1314,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="45">
     <cellStyle name="20% - Accent1 2" xfId="2" xr:uid="{29CE4DB6-59F3-44CE-84B5-F5680B9CB77A}"/>
@@ -1659,7 +1671,7 @@
     <col min="3" max="3" width="23.88671875" customWidth="1"/>
     <col min="4" max="4" width="13.109375" customWidth="1"/>
     <col min="5" max="5" width="55.5546875" customWidth="1"/>
-    <col min="6" max="6" width="158.44140625" style="8" customWidth="1"/>
+    <col min="6" max="6" width="82.5546875" style="8" customWidth="1"/>
     <col min="7" max="7" width="13.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1705,6 +1717,7 @@
       <c r="F2" s="7" t="s">
         <v>140</v>
       </c>
+      <c r="G2" s="14"/>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="2" t="s">
@@ -1718,6 +1731,9 @@
       </c>
       <c r="F3" s="8" t="s">
         <v>141</v>
+      </c>
+      <c r="G3" s="14" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="4" spans="1:7">
